--- a/حركات الشركات للبصريات - جديد/ARCD_Transactions_Optics.xlsx
+++ b/حركات الشركات للبصريات - جديد/ARCD_Transactions_Optics.xlsx
@@ -8,19 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Omar\waad_temp_website\حركات الشركات للبصريات - جديد\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B60C893-0877-42ED-8AF8-3D1B4719ED6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32CDE76D-5AC9-4612-AD86-DE49811AD688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="البصريات" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="62">
   <si>
     <t>اسم المريض</t>
   </si>
@@ -71,9 +82,6 @@
   </si>
   <si>
     <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>توفيق عبدالسلام المذبل</t>
   </si>
   <si>
     <t>ARCAD20250047M1</t>
@@ -215,7 +223,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -223,16 +231,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -240,12 +262,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -667,42 +707,42 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
       </c>
       <c r="D4">
         <v>500</v>
       </c>
       <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
       <c r="G4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>17</v>
+    <row r="5" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
         <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
       </c>
       <c r="D5">
         <v>500</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
@@ -713,19 +753,19 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
       </c>
       <c r="D6">
         <v>500</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -736,22 +776,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
         <v>30</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
       </c>
       <c r="D7">
         <v>400</v>
       </c>
       <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" t="s">
         <v>33</v>
-      </c>
-      <c r="F7" t="s">
-        <v>34</v>
       </c>
       <c r="G7" t="s">
         <v>12</v>
@@ -759,19 +799,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
         <v>35</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>36</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
       </c>
       <c r="D8">
         <v>270</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
@@ -782,19 +822,19 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
         <v>39</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>40</v>
-      </c>
-      <c r="C9" t="s">
-        <v>41</v>
       </c>
       <c r="D9">
         <v>500</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
@@ -805,22 +845,22 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
         <v>43</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>44</v>
-      </c>
-      <c r="C10" t="s">
-        <v>45</v>
       </c>
       <c r="D10">
         <v>500</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
         <v>12</v>
@@ -828,22 +868,22 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
         <v>47</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>48</v>
-      </c>
-      <c r="C11" t="s">
-        <v>49</v>
       </c>
       <c r="D11">
         <v>500</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G11" t="s">
         <v>12</v>
@@ -851,19 +891,19 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
         <v>51</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>52</v>
-      </c>
-      <c r="C12" t="s">
-        <v>53</v>
       </c>
       <c r="D12">
         <v>500</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
@@ -874,22 +914,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s">
         <v>55</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>56</v>
-      </c>
-      <c r="C13" t="s">
-        <v>57</v>
       </c>
       <c r="D13">
         <v>500</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G13" t="s">
         <v>12</v>
@@ -897,22 +937,22 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" t="s">
         <v>59</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>60</v>
-      </c>
-      <c r="C14" t="s">
-        <v>61</v>
       </c>
       <c r="D14">
         <v>500</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G14" t="s">
         <v>12</v>
